--- a/release-branch/StructureDefinition-bc-find-candidates-request-bundle.xlsx
+++ b/release-branch/StructureDefinition-bc-find-candidates-request-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-27T22:30:17+00:00</t>
+    <t>2025-10-07T21:05:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -361,7 +361,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -2378,7 +2378,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>121</v>
       </c>
@@ -3966,7 +3966,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
         <v>189</v>
       </c>
@@ -4080,7 +4080,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>193</v>
       </c>
@@ -4874,7 +4874,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>215</v>
       </c>
@@ -7022,7 +7022,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
         <v>267</v>
       </c>
@@ -7590,7 +7590,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
         <v>274</v>
       </c>
@@ -7704,7 +7704,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
         <v>275</v>
       </c>
@@ -8498,7 +8498,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
         <v>288</v>
       </c>
@@ -10646,7 +10646,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="81" hidden="true">
+    <row r="81">
       <c r="A81" t="s" s="2">
         <v>307</v>
       </c>
@@ -11214,7 +11214,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="86" hidden="true">
+    <row r="86">
       <c r="A86" t="s" s="2">
         <v>314</v>
       </c>
@@ -11328,7 +11328,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="87" hidden="true">
+    <row r="87">
       <c r="A87" t="s" s="2">
         <v>315</v>
       </c>
@@ -12124,7 +12124,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="94" hidden="true">
+    <row r="94">
       <c r="A94" t="s" s="2">
         <v>326</v>
       </c>
@@ -14272,7 +14272,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="113" hidden="true">
+    <row r="113">
       <c r="A113" t="s" s="2">
         <v>345</v>
       </c>
@@ -14840,7 +14840,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="118" hidden="true">
+    <row r="118">
       <c r="A118" t="s" s="2">
         <v>352</v>
       </c>
@@ -14954,7 +14954,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="119" hidden="true">
+    <row r="119">
       <c r="A119" t="s" s="2">
         <v>353</v>
       </c>
@@ -15748,7 +15748,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="126" hidden="true">
+    <row r="126">
       <c r="A126" t="s" s="2">
         <v>361</v>
       </c>
@@ -18014,12 +18014,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN145">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/release-branch/StructureDefinition-bc-find-candidates-request-bundle.xlsx
+++ b/release-branch/StructureDefinition-bc-find-candidates-request-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-07T21:05:34+00:00</t>
+    <t>2025-11-21T23:55:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/release-branch/StructureDefinition-bc-find-candidates-request-bundle.xlsx
+++ b/release-branch/StructureDefinition-bc-find-candidates-request-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-21T23:55:27+00:00</t>
+    <t>2026-01-12T21:43:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/release-branch/StructureDefinition-bc-find-candidates-request-bundle.xlsx
+++ b/release-branch/StructureDefinition-bc-find-candidates-request-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-12T21:43:07+00:00</t>
+    <t>2026-01-22T19:20:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/release-branch/StructureDefinition-bc-find-candidates-request-bundle.xlsx
+++ b/release-branch/StructureDefinition-bc-find-candidates-request-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-22T19:20:19+00:00</t>
+    <t>2026-02-17T21:23:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/release-branch/StructureDefinition-bc-find-candidates-request-bundle.xlsx
+++ b/release-branch/StructureDefinition-bc-find-candidates-request-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T21:23:45+00:00</t>
+    <t>2026-03-17T18:19:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/release-branch/StructureDefinition-bc-find-candidates-request-bundle.xlsx
+++ b/release-branch/StructureDefinition-bc-find-candidates-request-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T18:19:20+00:00</t>
+    <t>2026-03-25T21:29:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
